--- a/data/trans_orig/LAWTONBRODY_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONBRODY_2023-Habitat-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,46</t>
+          <t>6,52</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,14</t>
+          <t>6,18</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 6,77</t>
+          <t>6,18; 6,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,62; 6,12</t>
+          <t>5,61; 6,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 6,33</t>
+          <t>5,98; 6,39</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>6,92</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>6,11</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>6,45</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 7,12</t>
+          <t>6,62; 7,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 6,34</t>
+          <t>5,83; 6,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 6,62</t>
+          <t>6,24; 6,62</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>7,41</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,3</t>
+          <t>6,32</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,32</t>
+          <t>6,85</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 7,6</t>
+          <t>7,15; 7,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 7,82</t>
+          <t>5,97; 6,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,74; 7,76</t>
+          <t>6,6; 7,03</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,15</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,48</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>6,74</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 7,32</t>
+          <t>6,92; 7,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,24; 6,68</t>
+          <t>6,19; 6,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 6,9</t>
+          <t>6,56; 6,9</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>6,56</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,1</t>
+          <t>6,86; 7,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 7,35</t>
+          <t>6,08; 6,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,29</t>
+          <t>6,46; 6,65</t>
         </is>
       </c>
     </row>
